--- a/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
+++ b/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
@@ -5,10 +5,10 @@
   <sheets>
     <sheet name="MK III" sheetId="1" r:id="rId1"/>
     <sheet name="MK IV" sheetId="2" r:id="rId2"/>
-    <sheet name="MK 0" sheetId="3" r:id="rId3"/>
-    <sheet name="MK I" sheetId="4" r:id="rId4"/>
-    <sheet name="MK II" sheetId="5" r:id="rId5"/>
-    <sheet name="MK V" sheetId="6" r:id="rId6"/>
+    <sheet name="MK I" sheetId="3" r:id="rId3"/>
+    <sheet name="MK II" sheetId="4" r:id="rId4"/>
+    <sheet name="MK V" sheetId="5" r:id="rId5"/>
+    <sheet name="MK 0" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -8437,7 +8437,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J66"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8472,168 +8484,2088 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Bane 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Level 1</v>
+        <v>Infantry Lethality</v>
       </c>
       <c r="C2">
-        <v>0.01</v>
-      </c>
-      <c r="D2">
-        <v>0.01</v>
-      </c>
-      <c r="E2">
-        <v>0.01</v>
-      </c>
-      <c r="F2">
-        <v>0.01</v>
-      </c>
-      <c r="G2">
-        <v>0.01</v>
-      </c>
-      <c r="H2">
-        <v>0.01</v>
+        <v>0.006</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2">
+        <v>Construction Time</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Bane 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C3">
+        <v>0.006</v>
+      </c>
+      <c r="D3">
+        <v>0.006</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Bane 3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C4">
+        <v>0.006</v>
+      </c>
+      <c r="D4">
+        <v>0.006</v>
+      </c>
+      <c r="E4">
+        <v>0.006</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Bane 4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C5">
+        <v>0.006</v>
+      </c>
+      <c r="D5">
+        <v>0.006</v>
+      </c>
+      <c r="E5">
+        <v>0.006</v>
+      </c>
+      <c r="F5">
+        <v>0.006</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Bane 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C6">
+        <v>0.006</v>
+      </c>
+      <c r="D6">
+        <v>0.006</v>
+      </c>
+      <c r="E6">
+        <v>0.006</v>
+      </c>
+      <c r="F6">
+        <v>0.006</v>
+      </c>
+      <c r="G6">
+        <v>0.006</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Bane 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C7">
+        <v>0.006</v>
+      </c>
+      <c r="D7">
+        <v>0.006</v>
+      </c>
+      <c r="E7">
+        <v>0.006</v>
+      </c>
+      <c r="F7">
+        <v>0.006</v>
+      </c>
+      <c r="G7">
+        <v>0.006</v>
+      </c>
+      <c r="H7">
+        <v>0.006</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bane 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C8">
+        <v>0.012</v>
+      </c>
+      <c r="D8">
+        <v>0.006</v>
+      </c>
+      <c r="E8">
+        <v>0.006</v>
+      </c>
+      <c r="F8">
+        <v>0.006</v>
+      </c>
+      <c r="G8">
+        <v>0.006</v>
+      </c>
+      <c r="H8">
+        <v>0.006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Training Resources</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Bane 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C9">
+        <v>0.012</v>
+      </c>
+      <c r="D9">
+        <v>0.012</v>
+      </c>
+      <c r="E9">
+        <v>0.006</v>
+      </c>
+      <c r="F9">
+        <v>0.006</v>
+      </c>
+      <c r="G9">
+        <v>0.006</v>
+      </c>
+      <c r="H9">
+        <v>0.006</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Level 2</v>
-      </c>
-      <c r="C3">
-        <v>0.01</v>
-      </c>
-      <c r="D3">
-        <v>0.01</v>
-      </c>
-      <c r="E3">
-        <v>0.01</v>
-      </c>
-      <c r="F3">
-        <v>0.01</v>
-      </c>
-      <c r="G3">
-        <v>0.01</v>
-      </c>
-      <c r="H3">
-        <v>0.01</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3">
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Bane 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C10">
+        <v>0.012</v>
+      </c>
+      <c r="D10">
+        <v>0.012</v>
+      </c>
+      <c r="E10">
+        <v>0.012</v>
+      </c>
+      <c r="F10">
+        <v>0.006</v>
+      </c>
+      <c r="G10">
+        <v>0.006</v>
+      </c>
+      <c r="H10">
+        <v>0.006</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="J10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Bane 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C11">
+        <v>0.012</v>
+      </c>
+      <c r="D11">
+        <v>0.012</v>
+      </c>
+      <c r="E11">
+        <v>0.012</v>
+      </c>
+      <c r="F11">
+        <v>0.012</v>
+      </c>
+      <c r="G11">
+        <v>0.006</v>
+      </c>
+      <c r="H11">
+        <v>0.006</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="J11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Bane Ultra-Enhance</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C12">
+        <v>0.012</v>
+      </c>
+      <c r="D12">
+        <v>0.012</v>
+      </c>
+      <c r="E12">
+        <v>0.012</v>
+      </c>
+      <c r="F12">
+        <v>0.012</v>
+      </c>
+      <c r="G12">
+        <v>0.012</v>
+      </c>
+      <c r="H12">
+        <v>0.006</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Havoc I 1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>0.012</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Havoc I 2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>0.012</v>
+      </c>
+      <c r="H14">
+        <v>0.012</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="J14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Havoc I 3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C15">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15">
+        <v>0.012</v>
+      </c>
+      <c r="H15">
+        <v>0.012</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="J15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Havoc I 4</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C16">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D16">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16">
+        <v>0.012</v>
+      </c>
+      <c r="H16">
+        <v>0.012</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="J16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Havoc I 5</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17">
+        <v>0.012</v>
+      </c>
+      <c r="H17">
+        <v>0.012</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Level 3</v>
-      </c>
-      <c r="C4">
-        <v>0.01</v>
-      </c>
-      <c r="D4">
-        <v>0.01</v>
-      </c>
-      <c r="E4">
-        <v>0.01</v>
-      </c>
-      <c r="F4">
-        <v>0.01</v>
-      </c>
-      <c r="G4">
-        <v>0.01</v>
-      </c>
-      <c r="H4">
-        <v>0.01</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4">
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Havoc I 6</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G18">
+        <v>0.012</v>
+      </c>
+      <c r="H18">
+        <v>0.012</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="J18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Havoc I 7</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H19">
+        <v>0.012</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Havoc I 8</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="J20">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Havoc I 9</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C21">
+        <v>0.024</v>
+      </c>
+      <c r="D21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Havoc I 10</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C22">
+        <v>0.024</v>
+      </c>
+      <c r="D22">
+        <v>0.024</v>
+      </c>
+      <c r="E22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="J22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Havoc I Ultra-Enhance</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C23">
+        <v>0.024</v>
+      </c>
+      <c r="D23">
+        <v>0.024</v>
+      </c>
+      <c r="E23">
+        <v>0.024</v>
+      </c>
+      <c r="F23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Havoc II 1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>0.024</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Havoc II 2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>0.024</v>
+      </c>
+      <c r="F25">
+        <v>0.024</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Havoc II 3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>0.024</v>
+      </c>
+      <c r="F26">
+        <v>0.024</v>
+      </c>
+      <c r="G26">
+        <v>0.024</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26">
         <v>25</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Level 4</v>
-      </c>
-      <c r="C5">
-        <v>0.01</v>
-      </c>
-      <c r="D5">
-        <v>0.01</v>
-      </c>
-      <c r="E5">
-        <v>0.01</v>
-      </c>
-      <c r="F5">
-        <v>0.01</v>
-      </c>
-      <c r="G5">
-        <v>0.01</v>
-      </c>
-      <c r="H5">
-        <v>0.01</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5">
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Havoc II 4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>0.024</v>
+      </c>
+      <c r="F27">
+        <v>0.024</v>
+      </c>
+      <c r="G27">
+        <v>0.024</v>
+      </c>
+      <c r="H27">
+        <v>0.024</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="J27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Havoc II 5</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C28">
+        <v>0.03</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>0.024</v>
+      </c>
+      <c r="F28">
+        <v>0.024</v>
+      </c>
+      <c r="G28">
+        <v>0.024</v>
+      </c>
+      <c r="H28">
+        <v>0.024</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Havoc II 6</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C29">
+        <v>0.03</v>
+      </c>
+      <c r="D29">
+        <v>0.03</v>
+      </c>
+      <c r="E29">
+        <v>0.024</v>
+      </c>
+      <c r="F29">
+        <v>0.024</v>
+      </c>
+      <c r="G29">
+        <v>0.024</v>
+      </c>
+      <c r="H29">
+        <v>0.024</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="J29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Havoc II 7</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C30">
+        <v>0.03</v>
+      </c>
+      <c r="D30">
+        <v>0.03</v>
+      </c>
+      <c r="E30">
+        <v>0.03</v>
+      </c>
+      <c r="F30">
+        <v>0.024</v>
+      </c>
+      <c r="G30">
+        <v>0.024</v>
+      </c>
+      <c r="H30">
+        <v>0.024</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Havoc II 8</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C31">
+        <v>0.03</v>
+      </c>
+      <c r="D31">
+        <v>0.03</v>
+      </c>
+      <c r="E31">
+        <v>0.03</v>
+      </c>
+      <c r="F31">
+        <v>0.03</v>
+      </c>
+      <c r="G31">
+        <v>0.024</v>
+      </c>
+      <c r="H31">
+        <v>0.024</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="J31">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Havoc II 9</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C32">
+        <v>0.03</v>
+      </c>
+      <c r="D32">
+        <v>0.03</v>
+      </c>
+      <c r="E32">
+        <v>0.03</v>
+      </c>
+      <c r="F32">
+        <v>0.03</v>
+      </c>
+      <c r="G32">
+        <v>0.03</v>
+      </c>
+      <c r="H32">
+        <v>0.024</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Havoc II 10</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C33">
+        <v>0.03</v>
+      </c>
+      <c r="D33">
+        <v>0.03</v>
+      </c>
+      <c r="E33">
+        <v>0.03</v>
+      </c>
+      <c r="F33">
+        <v>0.03</v>
+      </c>
+      <c r="G33">
+        <v>0.03</v>
+      </c>
+      <c r="H33">
+        <v>0.03</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="J33">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Havoc II Ultra-Enhance</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C34">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D34">
+        <v>0.03</v>
+      </c>
+      <c r="E34">
+        <v>0.03</v>
+      </c>
+      <c r="F34">
+        <v>0.03</v>
+      </c>
+      <c r="G34">
+        <v>0.03</v>
+      </c>
+      <c r="H34">
+        <v>0.03</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Scourge I 1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C35">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Scourge I 2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C36">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D36">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Scourge I 3</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37">
         <v>30</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Level 5</v>
-      </c>
-      <c r="C6">
-        <v>0.01</v>
-      </c>
-      <c r="D6">
-        <v>0.01</v>
-      </c>
-      <c r="E6">
-        <v>0.01</v>
-      </c>
-      <c r="F6">
-        <v>0.01</v>
-      </c>
-      <c r="G6">
-        <v>0.01</v>
-      </c>
-      <c r="H6">
-        <v>0.01</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6">
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Scourge I 4</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="J38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Scourge I 5</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Scourge I 6</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Scourge I 7</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C41">
+        <v>0.042</v>
+      </c>
+      <c r="D41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="J41">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Scourge I 8</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C42">
+        <v>0.042</v>
+      </c>
+      <c r="D42">
+        <v>0.042</v>
+      </c>
+      <c r="E42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Scourge I 9</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C43">
+        <v>0.042</v>
+      </c>
+      <c r="D43">
+        <v>0.042</v>
+      </c>
+      <c r="E43">
+        <v>0.042</v>
+      </c>
+      <c r="F43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Scourge I 10</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C44">
+        <v>0.042</v>
+      </c>
+      <c r="D44">
+        <v>0.042</v>
+      </c>
+      <c r="E44">
+        <v>0.042</v>
+      </c>
+      <c r="F44">
+        <v>0.042</v>
+      </c>
+      <c r="G44">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H44">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="J44">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Scourge I Ultra-Enhance</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C45">
+        <v>0.042</v>
+      </c>
+      <c r="D45">
+        <v>0.042</v>
+      </c>
+      <c r="E45">
+        <v>0.042</v>
+      </c>
+      <c r="F45">
+        <v>0.042</v>
+      </c>
+      <c r="G45">
+        <v>0.042</v>
+      </c>
+      <c r="H45">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Scourge II 1</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46">
+        <v>0.042</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Scourge II 2</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47">
+        <v>0.042</v>
+      </c>
+      <c r="H47">
+        <v>0.042</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Scourge II 3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C48">
+        <v>0.048</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48">
+        <v>0.042</v>
+      </c>
+      <c r="H48">
+        <v>0.042</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="J48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Scourge II 4</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C49">
+        <v>0.048</v>
+      </c>
+      <c r="D49">
+        <v>0.048</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49">
+        <v>0.042</v>
+      </c>
+      <c r="H49">
+        <v>0.042</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49">
         <v>35</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Scourge II 5</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C50">
+        <v>0.048</v>
+      </c>
+      <c r="D50">
+        <v>0.048</v>
+      </c>
+      <c r="E50">
+        <v>0.048</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50">
+        <v>0.042</v>
+      </c>
+      <c r="H50">
+        <v>0.042</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Scourge II 6</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C51">
+        <v>0.048</v>
+      </c>
+      <c r="D51">
+        <v>0.048</v>
+      </c>
+      <c r="E51">
+        <v>0.048</v>
+      </c>
+      <c r="F51">
+        <v>0.048</v>
+      </c>
+      <c r="G51">
+        <v>0.042</v>
+      </c>
+      <c r="H51">
+        <v>0.042</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="J51">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Scourge II 7</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C52">
+        <v>0.048</v>
+      </c>
+      <c r="D52">
+        <v>0.048</v>
+      </c>
+      <c r="E52">
+        <v>0.048</v>
+      </c>
+      <c r="F52">
+        <v>0.048</v>
+      </c>
+      <c r="G52">
+        <v>0.048</v>
+      </c>
+      <c r="H52">
+        <v>0.042</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Scourge II 8</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C53">
+        <v>0.048</v>
+      </c>
+      <c r="D53">
+        <v>0.048</v>
+      </c>
+      <c r="E53">
+        <v>0.048</v>
+      </c>
+      <c r="F53">
+        <v>0.048</v>
+      </c>
+      <c r="G53">
+        <v>0.048</v>
+      </c>
+      <c r="H53">
+        <v>0.048</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Scourge II 9</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C54">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D54">
+        <v>0.048</v>
+      </c>
+      <c r="E54">
+        <v>0.048</v>
+      </c>
+      <c r="F54">
+        <v>0.048</v>
+      </c>
+      <c r="G54">
+        <v>0.048</v>
+      </c>
+      <c r="H54">
+        <v>0.048</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="J54">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Scourge II 10</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C55">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D55">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="E55">
+        <v>0.048</v>
+      </c>
+      <c r="F55">
+        <v>0.048</v>
+      </c>
+      <c r="G55">
+        <v>0.048</v>
+      </c>
+      <c r="H55">
+        <v>0.048</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Scourge II Ultra-Enhance</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="E56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F56">
+        <v>0.048</v>
+      </c>
+      <c r="G56">
+        <v>0.048</v>
+      </c>
+      <c r="H56">
+        <v>0.048</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Scourge III 1</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Scourge III 2</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F58">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="J58">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Scourge III 3</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Scourge III 4</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Scourge III 5</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C61">
+        <v>0.06</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="J61">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Scourge III 6</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C62">
+        <v>0.06</v>
+      </c>
+      <c r="D62">
+        <v>0.06</v>
+      </c>
+      <c r="E62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Scourge III 7</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C63">
+        <v>0.06</v>
+      </c>
+      <c r="D63">
+        <v>0.06</v>
+      </c>
+      <c r="E63">
+        <v>0.06</v>
+      </c>
+      <c r="F63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I63" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="J63">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Scourge III 8</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C64">
+        <v>0.06</v>
+      </c>
+      <c r="D64">
+        <v>0.06</v>
+      </c>
+      <c r="E64">
+        <v>0.06</v>
+      </c>
+      <c r="F64">
+        <v>0.06</v>
+      </c>
+      <c r="G64">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H64">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Scourge III 9</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C65">
+        <v>0.06</v>
+      </c>
+      <c r="D65">
+        <v>0.06</v>
+      </c>
+      <c r="E65">
+        <v>0.06</v>
+      </c>
+      <c r="F65">
+        <v>0.06</v>
+      </c>
+      <c r="G65">
+        <v>0.06</v>
+      </c>
+      <c r="H65">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="J65">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Scourge III 10</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C66">
+        <v>0.06</v>
+      </c>
+      <c r="D66">
+        <v>0.06</v>
+      </c>
+      <c r="E66">
+        <v>0.06</v>
+      </c>
+      <c r="F66">
+        <v>0.06</v>
+      </c>
+      <c r="G66">
+        <v>0.06</v>
+      </c>
+      <c r="H66">
+        <v>0.06</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Adapt &amp; Overcome</v>
+      </c>
+      <c r="J66">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
+++ b/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
@@ -5,10 +5,10 @@
   <sheets>
     <sheet name="MK III" sheetId="1" r:id="rId1"/>
     <sheet name="MK IV" sheetId="2" r:id="rId2"/>
-    <sheet name="MK I" sheetId="3" r:id="rId3"/>
-    <sheet name="MK II" sheetId="4" r:id="rId4"/>
-    <sheet name="MK V" sheetId="5" r:id="rId5"/>
-    <sheet name="MK 0" sheetId="6" r:id="rId6"/>
+    <sheet name="MK V" sheetId="3" r:id="rId3"/>
+    <sheet name="MK 0" sheetId="4" r:id="rId4"/>
+    <sheet name="MK I" sheetId="5" r:id="rId5"/>
+    <sheet name="MK II" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -8031,7 +8031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8066,175 +8066,2095 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Bane 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Level 1</v>
+        <v>Infantry Lethality</v>
       </c>
       <c r="C2">
-        <v>0.01</v>
-      </c>
-      <c r="D2">
-        <v>0.01</v>
-      </c>
-      <c r="E2">
-        <v>0.01</v>
-      </c>
-      <c r="F2">
-        <v>0.01</v>
-      </c>
-      <c r="G2">
-        <v>0.01</v>
-      </c>
-      <c r="H2">
-        <v>0.01</v>
+        <v>0.006</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2">
+        <v>Construction Time</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Bane 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C3">
+        <v>0.006</v>
+      </c>
+      <c r="D3">
+        <v>0.006</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Bane 3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C4">
+        <v>0.006</v>
+      </c>
+      <c r="D4">
+        <v>0.006</v>
+      </c>
+      <c r="E4">
+        <v>0.006</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Bane 4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C5">
+        <v>0.006</v>
+      </c>
+      <c r="D5">
+        <v>0.006</v>
+      </c>
+      <c r="E5">
+        <v>0.006</v>
+      </c>
+      <c r="F5">
+        <v>0.006</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Bane 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C6">
+        <v>0.006</v>
+      </c>
+      <c r="D6">
+        <v>0.006</v>
+      </c>
+      <c r="E6">
+        <v>0.006</v>
+      </c>
+      <c r="F6">
+        <v>0.006</v>
+      </c>
+      <c r="G6">
+        <v>0.006</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Bane 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C7">
+        <v>0.006</v>
+      </c>
+      <c r="D7">
+        <v>0.006</v>
+      </c>
+      <c r="E7">
+        <v>0.006</v>
+      </c>
+      <c r="F7">
+        <v>0.006</v>
+      </c>
+      <c r="G7">
+        <v>0.006</v>
+      </c>
+      <c r="H7">
+        <v>0.006</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bane 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C8">
+        <v>0.012</v>
+      </c>
+      <c r="D8">
+        <v>0.006</v>
+      </c>
+      <c r="E8">
+        <v>0.006</v>
+      </c>
+      <c r="F8">
+        <v>0.006</v>
+      </c>
+      <c r="G8">
+        <v>0.006</v>
+      </c>
+      <c r="H8">
+        <v>0.006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Training Resources</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Bane 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C9">
+        <v>0.012</v>
+      </c>
+      <c r="D9">
+        <v>0.012</v>
+      </c>
+      <c r="E9">
+        <v>0.006</v>
+      </c>
+      <c r="F9">
+        <v>0.006</v>
+      </c>
+      <c r="G9">
+        <v>0.006</v>
+      </c>
+      <c r="H9">
+        <v>0.006</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Level 2</v>
-      </c>
-      <c r="C3">
-        <v>0.01</v>
-      </c>
-      <c r="D3">
-        <v>0.01</v>
-      </c>
-      <c r="E3">
-        <v>0.01</v>
-      </c>
-      <c r="F3">
-        <v>0.01</v>
-      </c>
-      <c r="G3">
-        <v>0.01</v>
-      </c>
-      <c r="H3">
-        <v>0.01</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3">
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Bane 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C10">
+        <v>0.012</v>
+      </c>
+      <c r="D10">
+        <v>0.012</v>
+      </c>
+      <c r="E10">
+        <v>0.012</v>
+      </c>
+      <c r="F10">
+        <v>0.006</v>
+      </c>
+      <c r="G10">
+        <v>0.006</v>
+      </c>
+      <c r="H10">
+        <v>0.006</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="J10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Bane 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C11">
+        <v>0.012</v>
+      </c>
+      <c r="D11">
+        <v>0.012</v>
+      </c>
+      <c r="E11">
+        <v>0.012</v>
+      </c>
+      <c r="F11">
+        <v>0.012</v>
+      </c>
+      <c r="G11">
+        <v>0.006</v>
+      </c>
+      <c r="H11">
+        <v>0.006</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="J11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Bane Ultra-Enhance</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C12">
+        <v>0.012</v>
+      </c>
+      <c r="D12">
+        <v>0.012</v>
+      </c>
+      <c r="E12">
+        <v>0.012</v>
+      </c>
+      <c r="F12">
+        <v>0.012</v>
+      </c>
+      <c r="G12">
+        <v>0.012</v>
+      </c>
+      <c r="H12">
+        <v>0.006</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Havoc I 1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>0.012</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Havoc I 2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>0.012</v>
+      </c>
+      <c r="H14">
+        <v>0.012</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="J14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Havoc I 3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C15">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15">
+        <v>0.012</v>
+      </c>
+      <c r="H15">
+        <v>0.012</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="J15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Havoc I 4</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C16">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D16">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16">
+        <v>0.012</v>
+      </c>
+      <c r="H16">
+        <v>0.012</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="J16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Havoc I 5</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E17">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17">
+        <v>0.012</v>
+      </c>
+      <c r="H17">
+        <v>0.012</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Level 3</v>
-      </c>
-      <c r="C4">
-        <v>0.01</v>
-      </c>
-      <c r="D4">
-        <v>0.01</v>
-      </c>
-      <c r="E4">
-        <v>0.01</v>
-      </c>
-      <c r="F4">
-        <v>0.01</v>
-      </c>
-      <c r="G4">
-        <v>0.01</v>
-      </c>
-      <c r="H4">
-        <v>0.01</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4">
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Havoc I 6</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F18">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G18">
+        <v>0.012</v>
+      </c>
+      <c r="H18">
+        <v>0.012</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="J18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Havoc I 7</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G19">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H19">
+        <v>0.012</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Havoc I 8</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="D20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H20">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="J20">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Havoc I 9</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C21">
+        <v>0.024</v>
+      </c>
+      <c r="D21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H21">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Havoc I 10</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C22">
+        <v>0.024</v>
+      </c>
+      <c r="D22">
+        <v>0.024</v>
+      </c>
+      <c r="E22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="F22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H22">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="J22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Havoc I Ultra-Enhance</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C23">
+        <v>0.024</v>
+      </c>
+      <c r="D23">
+        <v>0.024</v>
+      </c>
+      <c r="E23">
+        <v>0.024</v>
+      </c>
+      <c r="F23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="G23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H23">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Havoc II 1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>0.024</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Havoc II 2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>0.024</v>
+      </c>
+      <c r="F25">
+        <v>0.024</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Havoc II 3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>0.024</v>
+      </c>
+      <c r="F26">
+        <v>0.024</v>
+      </c>
+      <c r="G26">
+        <v>0.024</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26">
         <v>25</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Level 4</v>
-      </c>
-      <c r="C5">
-        <v>0.01</v>
-      </c>
-      <c r="D5">
-        <v>0.01</v>
-      </c>
-      <c r="E5">
-        <v>0.01</v>
-      </c>
-      <c r="F5">
-        <v>0.01</v>
-      </c>
-      <c r="G5">
-        <v>0.01</v>
-      </c>
-      <c r="H5">
-        <v>0.01</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5">
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Havoc II 4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>0.024</v>
+      </c>
+      <c r="F27">
+        <v>0.024</v>
+      </c>
+      <c r="G27">
+        <v>0.024</v>
+      </c>
+      <c r="H27">
+        <v>0.024</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="J27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Havoc II 5</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C28">
+        <v>0.03</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>0.024</v>
+      </c>
+      <c r="F28">
+        <v>0.024</v>
+      </c>
+      <c r="G28">
+        <v>0.024</v>
+      </c>
+      <c r="H28">
+        <v>0.024</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Havoc II 6</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C29">
+        <v>0.03</v>
+      </c>
+      <c r="D29">
+        <v>0.03</v>
+      </c>
+      <c r="E29">
+        <v>0.024</v>
+      </c>
+      <c r="F29">
+        <v>0.024</v>
+      </c>
+      <c r="G29">
+        <v>0.024</v>
+      </c>
+      <c r="H29">
+        <v>0.024</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="J29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Havoc II 7</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C30">
+        <v>0.03</v>
+      </c>
+      <c r="D30">
+        <v>0.03</v>
+      </c>
+      <c r="E30">
+        <v>0.03</v>
+      </c>
+      <c r="F30">
+        <v>0.024</v>
+      </c>
+      <c r="G30">
+        <v>0.024</v>
+      </c>
+      <c r="H30">
+        <v>0.024</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Havoc II 8</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C31">
+        <v>0.03</v>
+      </c>
+      <c r="D31">
+        <v>0.03</v>
+      </c>
+      <c r="E31">
+        <v>0.03</v>
+      </c>
+      <c r="F31">
+        <v>0.03</v>
+      </c>
+      <c r="G31">
+        <v>0.024</v>
+      </c>
+      <c r="H31">
+        <v>0.024</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="J31">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Havoc II 9</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C32">
+        <v>0.03</v>
+      </c>
+      <c r="D32">
+        <v>0.03</v>
+      </c>
+      <c r="E32">
+        <v>0.03</v>
+      </c>
+      <c r="F32">
+        <v>0.03</v>
+      </c>
+      <c r="G32">
+        <v>0.03</v>
+      </c>
+      <c r="H32">
+        <v>0.024</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Havoc II 10</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C33">
+        <v>0.03</v>
+      </c>
+      <c r="D33">
+        <v>0.03</v>
+      </c>
+      <c r="E33">
+        <v>0.03</v>
+      </c>
+      <c r="F33">
+        <v>0.03</v>
+      </c>
+      <c r="G33">
+        <v>0.03</v>
+      </c>
+      <c r="H33">
+        <v>0.03</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="J33">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Havoc II Ultra-Enhance</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C34">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D34">
+        <v>0.03</v>
+      </c>
+      <c r="E34">
+        <v>0.03</v>
+      </c>
+      <c r="F34">
+        <v>0.03</v>
+      </c>
+      <c r="G34">
+        <v>0.03</v>
+      </c>
+      <c r="H34">
+        <v>0.03</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Scourge I 1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C35">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Scourge I 2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C36">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D36">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Scourge I 3</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E37">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37">
         <v>30</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Level 5</v>
-      </c>
-      <c r="C6">
-        <v>0.01</v>
-      </c>
-      <c r="D6">
-        <v>0.01</v>
-      </c>
-      <c r="E6">
-        <v>0.01</v>
-      </c>
-      <c r="F6">
-        <v>0.01</v>
-      </c>
-      <c r="G6">
-        <v>0.01</v>
-      </c>
-      <c r="H6">
-        <v>0.01</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6">
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Scourge I 4</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F38">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="J38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Scourge I 5</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G39">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Scourge I 6</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="D40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H40">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Scourge I 7</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C41">
+        <v>0.042</v>
+      </c>
+      <c r="D41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H41">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="J41">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Scourge I 8</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C42">
+        <v>0.042</v>
+      </c>
+      <c r="D42">
+        <v>0.042</v>
+      </c>
+      <c r="E42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="F42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H42">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Scourge I 9</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C43">
+        <v>0.042</v>
+      </c>
+      <c r="D43">
+        <v>0.042</v>
+      </c>
+      <c r="E43">
+        <v>0.042</v>
+      </c>
+      <c r="F43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="G43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H43">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Scourge I 10</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C44">
+        <v>0.042</v>
+      </c>
+      <c r="D44">
+        <v>0.042</v>
+      </c>
+      <c r="E44">
+        <v>0.042</v>
+      </c>
+      <c r="F44">
+        <v>0.042</v>
+      </c>
+      <c r="G44">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="H44">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="J44">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Scourge I Ultra-Enhance</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C45">
+        <v>0.042</v>
+      </c>
+      <c r="D45">
+        <v>0.042</v>
+      </c>
+      <c r="E45">
+        <v>0.042</v>
+      </c>
+      <c r="F45">
+        <v>0.042</v>
+      </c>
+      <c r="G45">
+        <v>0.042</v>
+      </c>
+      <c r="H45">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Scourge II 1</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46">
+        <v>0.042</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Scourge II 2</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47">
+        <v>0.042</v>
+      </c>
+      <c r="H47">
+        <v>0.042</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Scourge II 3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C48">
+        <v>0.048</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48">
+        <v>0.042</v>
+      </c>
+      <c r="H48">
+        <v>0.042</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="J48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Scourge II 4</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C49">
+        <v>0.048</v>
+      </c>
+      <c r="D49">
+        <v>0.048</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49">
+        <v>0.042</v>
+      </c>
+      <c r="H49">
+        <v>0.042</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49">
         <v>35</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Scourge II 5</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C50">
+        <v>0.048</v>
+      </c>
+      <c r="D50">
+        <v>0.048</v>
+      </c>
+      <c r="E50">
+        <v>0.048</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50">
+        <v>0.042</v>
+      </c>
+      <c r="H50">
+        <v>0.042</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Scourge II 6</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C51">
+        <v>0.048</v>
+      </c>
+      <c r="D51">
+        <v>0.048</v>
+      </c>
+      <c r="E51">
+        <v>0.048</v>
+      </c>
+      <c r="F51">
+        <v>0.048</v>
+      </c>
+      <c r="G51">
+        <v>0.042</v>
+      </c>
+      <c r="H51">
+        <v>0.042</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="J51">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Scourge II 7</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C52">
+        <v>0.048</v>
+      </c>
+      <c r="D52">
+        <v>0.048</v>
+      </c>
+      <c r="E52">
+        <v>0.048</v>
+      </c>
+      <c r="F52">
+        <v>0.048</v>
+      </c>
+      <c r="G52">
+        <v>0.048</v>
+      </c>
+      <c r="H52">
+        <v>0.042</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Scourge II 8</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C53">
+        <v>0.048</v>
+      </c>
+      <c r="D53">
+        <v>0.048</v>
+      </c>
+      <c r="E53">
+        <v>0.048</v>
+      </c>
+      <c r="F53">
+        <v>0.048</v>
+      </c>
+      <c r="G53">
+        <v>0.048</v>
+      </c>
+      <c r="H53">
+        <v>0.048</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Scourge II 9</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C54">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D54">
+        <v>0.048</v>
+      </c>
+      <c r="E54">
+        <v>0.048</v>
+      </c>
+      <c r="F54">
+        <v>0.048</v>
+      </c>
+      <c r="G54">
+        <v>0.048</v>
+      </c>
+      <c r="H54">
+        <v>0.048</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="J54">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Scourge II 10</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C55">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D55">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="E55">
+        <v>0.048</v>
+      </c>
+      <c r="F55">
+        <v>0.048</v>
+      </c>
+      <c r="G55">
+        <v>0.048</v>
+      </c>
+      <c r="H55">
+        <v>0.048</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Scourge II Ultra-Enhance</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="D56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="E56">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F56">
+        <v>0.048</v>
+      </c>
+      <c r="G56">
+        <v>0.048</v>
+      </c>
+      <c r="H56">
+        <v>0.048</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Scourge III 1</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Scourge III 2</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F58">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="J58">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Scourge III 3</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G59">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Scourge III 4</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H60">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Scourge III 5</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C61">
+        <v>0.06</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H61">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="J61">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Scourge III 6</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C62">
+        <v>0.06</v>
+      </c>
+      <c r="D62">
+        <v>0.06</v>
+      </c>
+      <c r="E62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="F62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H62">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Scourge III 7</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C63">
+        <v>0.06</v>
+      </c>
+      <c r="D63">
+        <v>0.06</v>
+      </c>
+      <c r="E63">
+        <v>0.06</v>
+      </c>
+      <c r="F63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="G63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H63">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I63" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="J63">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Scourge III 8</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C64">
+        <v>0.06</v>
+      </c>
+      <c r="D64">
+        <v>0.06</v>
+      </c>
+      <c r="E64">
+        <v>0.06</v>
+      </c>
+      <c r="F64">
+        <v>0.06</v>
+      </c>
+      <c r="G64">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="H64">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Scourge III 9</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C65">
+        <v>0.06</v>
+      </c>
+      <c r="D65">
+        <v>0.06</v>
+      </c>
+      <c r="E65">
+        <v>0.06</v>
+      </c>
+      <c r="F65">
+        <v>0.06</v>
+      </c>
+      <c r="G65">
+        <v>0.06</v>
+      </c>
+      <c r="H65">
+        <v>0.054000000000000006</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="J65">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Scourge III 10</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C66">
+        <v>0.06</v>
+      </c>
+      <c r="D66">
+        <v>0.06</v>
+      </c>
+      <c r="E66">
+        <v>0.06</v>
+      </c>
+      <c r="F66">
+        <v>0.06</v>
+      </c>
+      <c r="G66">
+        <v>0.06</v>
+      </c>
+      <c r="H66">
+        <v>0.06</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Adapt &amp; Overcome</v>
+      </c>
+      <c r="J66">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J132"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8269,175 +10189,4207 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Bane 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Level 1</v>
-      </c>
-      <c r="C2">
-        <v>0.01</v>
-      </c>
-      <c r="D2">
-        <v>0.01</v>
-      </c>
-      <c r="E2">
-        <v>0.01</v>
-      </c>
-      <c r="F2">
-        <v>0.01</v>
-      </c>
-      <c r="G2">
-        <v>0.01</v>
-      </c>
-      <c r="H2">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Artillery Barrage</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>Bane 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Level 2</v>
-      </c>
-      <c r="C3">
-        <v>0.01</v>
-      </c>
-      <c r="D3">
-        <v>0.01</v>
-      </c>
-      <c r="E3">
-        <v>0.01</v>
-      </c>
-      <c r="F3">
-        <v>0.01</v>
-      </c>
-      <c r="G3">
-        <v>0.01</v>
-      </c>
-      <c r="H3">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>Bane 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Level 3</v>
-      </c>
-      <c r="C4">
-        <v>0.01</v>
-      </c>
-      <c r="D4">
-        <v>0.01</v>
-      </c>
-      <c r="E4">
-        <v>0.01</v>
-      </c>
-      <c r="F4">
-        <v>0.01</v>
-      </c>
-      <c r="G4">
-        <v>0.01</v>
-      </c>
-      <c r="H4">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Rapid Fire</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>Bane 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Level 4</v>
-      </c>
-      <c r="C5">
-        <v>0.01</v>
-      </c>
-      <c r="D5">
-        <v>0.01</v>
-      </c>
-      <c r="E5">
-        <v>0.01</v>
-      </c>
-      <c r="F5">
-        <v>0.01</v>
-      </c>
-      <c r="G5">
-        <v>0.01</v>
-      </c>
-      <c r="H5">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>Bane 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Level 5</v>
-      </c>
-      <c r="C6">
-        <v>0.01</v>
-      </c>
-      <c r="D6">
-        <v>0.01</v>
-      </c>
-      <c r="E6">
-        <v>0.01</v>
-      </c>
-      <c r="F6">
-        <v>0.01</v>
-      </c>
-      <c r="G6">
-        <v>0.01</v>
-      </c>
-      <c r="H6">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>5709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Bane 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Suppressive Barrage</v>
+      </c>
+      <c r="J7">
+        <v>6569</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bane 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
+        <v>7449</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Bane 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
+        <v>8360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Bane 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10">
+        <v>9221</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Bane 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11">
+        <v>10103</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Bane Ultra-Enhance</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>10962</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Havoc I 1</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Destructive Missile</v>
+      </c>
+      <c r="J13">
+        <v>10940</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Havoc I 2</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
+        <v>11815</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Havoc I 3</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Infantry Recharge</v>
+      </c>
+      <c r="J15">
+        <v>12685</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Havoc I 4</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16">
+        <v>13565</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Havoc I 5</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
+        <v>14455</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Havoc I 6</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Rider Recharge</v>
+      </c>
+      <c r="J18">
+        <v>15335</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Havoc I 7</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19">
+        <v>16106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Havoc I 8</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20">
+        <v>16996</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Havoc I 9</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Hunter Recharge</v>
+      </c>
+      <c r="J21">
+        <v>17877</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Havoc I 10</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22">
+        <v>18767</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Havoc I Ultra-Enhance</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Quick Recharge</v>
+      </c>
+      <c r="J23">
+        <v>19148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Havoc II 1</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24">
+        <v>19130</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Havoc II 2</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25">
+        <v>19648</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Havoc II 3</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Target: Infantry</v>
+      </c>
+      <c r="J26">
+        <v>20028</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Havoc II 4</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27">
+        <v>20529</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Havoc II 5</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Target: Riders</v>
+      </c>
+      <c r="J28">
+        <v>20919</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Havoc II 6</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29">
+        <v>21309</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Havoc II 7</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Target: Hunters</v>
+      </c>
+      <c r="J30">
+        <v>21799</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Havoc II 8</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31">
+        <v>22190</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Havoc II 9</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Core Destruction</v>
+      </c>
+      <c r="J32">
+        <v>22690</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Havoc II 10</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33">
+        <v>23081</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Havoc II Ultra-Enhance</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34">
+        <v>23475</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Scourge I 1</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Electromagnetic Protection</v>
+      </c>
+      <c r="J35">
+        <v>23440</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Scourge I 2</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36">
+        <v>23963</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Scourge I 3</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37">
+        <v>24343</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Scourge I 4</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Infantry Induction</v>
+      </c>
+      <c r="J38">
+        <v>24844</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Scourge I 5</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39">
+        <v>25234</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Scourge I 6</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40">
+        <v>25733</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Scourge I 7</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41">
+        <v>26115</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Scourge I 8</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>Rider Induction</v>
+      </c>
+      <c r="J42">
+        <v>26615</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Scourge I 9</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43">
+        <v>27006</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Scourge I 10</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44">
+        <v>27397</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Scourge I Ultra-Enhance</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>Hunter Induction</v>
+      </c>
+      <c r="J45">
+        <v>27768</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Scourge II 1</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46">
+        <v>27740</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Scourge II 2</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47">
+        <v>28158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Scourge II 3</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48">
+        <v>28539</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Scourge II 4</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>High Voltage</v>
+      </c>
+      <c r="J49">
+        <v>29029</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Scourge II 5</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50">
+        <v>29409</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Scourge II 6</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51">
+        <v>29789</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Scourge II 7</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52">
+        <v>30180</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Scourge II 8</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Infantry Protection</v>
+      </c>
+      <c r="J53">
+        <v>30550</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Scourge II 9</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54">
+        <v>30941</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Scourge II 10</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55">
+        <v>31322</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Scourge II Ultra-Enhance</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>Rider Protection</v>
+      </c>
+      <c r="J56">
+        <v>31705</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Scourge III 1</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57">
+        <v>31670</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Scourge III 2</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58">
+        <v>32087</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Scourge III 3</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59">
+        <v>32469</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Scourge III 4</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>Hunter Protection</v>
+      </c>
+      <c r="J60">
+        <v>32971</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Scourge III 5</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Scourge III 6</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62">
+        <v>33738</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Scourge III 7</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63">
+        <v>34122</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Scourge III 8</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>Core Reinforcement</v>
+      </c>
+      <c r="J64">
+        <v>34507</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Scourge III 9</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65">
+        <v>34893</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Scourge III 10</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66">
+        <v>35286</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Scourge III Ultra-Enhance</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67">
+        <v>35610</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Cataclysm I 1</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v>Dominating Aura</v>
+      </c>
+      <c r="J68">
+        <v>35460</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Cataclysm I 2</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69">
+        <v>35680</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Cataclysm I 3</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v>Hunting Aura</v>
+      </c>
+      <c r="J70">
+        <v>35930</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Cataclysm I 4</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71">
+        <v>36181</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Cataclysm I 5</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72">
+        <v>36432</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Cataclysm I 6</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v>Charging Aura</v>
+      </c>
+      <c r="J73">
+        <v>36563</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Cataclysm I 7</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74">
+        <v>36814</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Cataclysm I 8</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75">
+        <v>37065</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Cataclysm I 9</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v>Shooting Aura</v>
+      </c>
+      <c r="J76">
+        <v>37207</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Cataclysm I 10</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77">
+        <v>37451</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Cataclysm I Ultra-Enhance</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v>Piercing Aura</v>
+      </c>
+      <c r="J78">
+        <v>37706</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Cataclysm II 1</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79">
+        <v>37610</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Cataclysm II 2</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80">
+        <v>37846</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Cataclysm II 3</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v>Rapid Concentration</v>
+      </c>
+      <c r="J81">
+        <v>38097</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Cataclysm II 4</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82">
+        <v>38348</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Cataclysm II 5</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83">
+        <v>38489</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Cataclysm II 6</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v>Buffer Aura</v>
+      </c>
+      <c r="J84">
+        <v>38740</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Cataclysm II 7</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85">
+        <v>38991</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Cataclysm II 8</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86">
+        <v>39233</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Cataclysm II 9</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v>Cover Aura</v>
+      </c>
+      <c r="J87">
+        <v>39375</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Cataclysm II 10</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88">
+        <v>39630</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Cataclysm II Ultra-Enhance</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v>Protection Aura</v>
+      </c>
+      <c r="J89">
+        <v>39890</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Cataclysm III 1</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90">
+        <v>39770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Cataclysm III 2</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91">
+        <v>40025</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Cataclysm III 3</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92">
+        <v>40281</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Cataclysm III 4</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v>Precise Reinforcement</v>
+      </c>
+      <c r="J93">
+        <v>40419</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Cataclysm III 5</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94">
+        <v>40678</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Cataclysm III 6</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95">
+        <v>40829</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Cataclysm III 7</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96">
+        <v>41083</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Cataclysm III 8</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>Corrosion Aura</v>
+      </c>
+      <c r="J97">
+        <v>41239</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Cataclysm III 9</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98">
+        <v>41498</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Cataclysm III 10</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99">
+        <v>41790</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Cataclysm III Ultra-Enhance</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100">
+        <v>42190</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Abaddon I 1</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101">
+        <v>41670</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Abaddon I 2</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v>Destructive Ray</v>
+      </c>
+      <c r="J102">
+        <v>42072</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Abaddon I 3</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v>Infantry Concentration</v>
+      </c>
+      <c r="J103">
+        <v>42323</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Abaddon I 4</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104">
+        <v>42564</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Abaddon I 5</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105">
+        <v>42706</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Abaddon I 6</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v>Rider Concentration</v>
+      </c>
+      <c r="J106">
+        <v>42948</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Abaddon I 7</v>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107">
+        <v>43091</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Abaddon I 8</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108">
+        <v>43334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Abaddon I 9</v>
+      </c>
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v>Hunter Concentration</v>
+      </c>
+      <c r="J109">
+        <v>43479</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Abaddon I 10</v>
+      </c>
+      <c r="B110" t="str">
+        <v/>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110">
+        <v>43726</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Abaddon I Ultra-Enhance</v>
+      </c>
+      <c r="B111" t="str">
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v>Deep Burn</v>
+      </c>
+      <c r="J111">
+        <v>43872</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Abaddon II 1</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112">
+        <v>43570</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Abaddon II 2</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113">
+        <v>43993</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Abaddon II 3</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v>Energy Reserves</v>
+      </c>
+      <c r="J114">
+        <v>44124</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Abaddon II 4</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115">
+        <v>44191</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Abaddon II 5</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116">
+        <v>44258</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Abaddon II 6</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>Infantry Block</v>
+      </c>
+      <c r="J117">
+        <v>44390</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Abaddon II 7</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118">
+        <v>44513</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Abaddon II 8</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119">
+        <v>44647</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Abaddon II 9</v>
+      </c>
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>Rider Block</v>
+      </c>
+      <c r="J120">
+        <v>44772</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Abaddon II 10</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121">
+        <v>44856</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Abaddon II Ultra-Enhance</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122">
+        <v>44938</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Abaddon III 1</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123">
+        <v>44590</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Abaddon III 2</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124">
+        <v>45070</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Abaddon III 3</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125">
+        <v>45191</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Abaddon III 4</v>
+      </c>
+      <c r="B126" t="str">
+        <v/>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>Thermal Insulation</v>
+      </c>
+      <c r="J126">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Abaddon III 5</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127">
+        <v>45445</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Abaddon III 6</v>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128">
+        <v>45513</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Abaddon III 7</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129">
+        <v>45592</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Abaddon III 8</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130">
+        <v>45716</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Abaddon III 9</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131">
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Abaddon III 10</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v>Ray Dilution</v>
+      </c>
+      <c r="J132">
+        <v>45978</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J132"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -8447,7 +14399,7 @@
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8483,2089 +14435,9 @@
         <v>Fragments Required</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Bane 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C2">
-        <v>0.006</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>Construction Time</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Bane 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C3">
-        <v>0.006</v>
-      </c>
-      <c r="D3">
-        <v>0.006</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>Research Progress</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Bane 3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C4">
-        <v>0.006</v>
-      </c>
-      <c r="D4">
-        <v>0.006</v>
-      </c>
-      <c r="E4">
-        <v>0.006</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Speedy Training</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Bane 4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C5">
-        <v>0.006</v>
-      </c>
-      <c r="D5">
-        <v>0.006</v>
-      </c>
-      <c r="E5">
-        <v>0.006</v>
-      </c>
-      <c r="F5">
-        <v>0.006</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Wood Gathering</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Bane 5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C6">
-        <v>0.006</v>
-      </c>
-      <c r="D6">
-        <v>0.006</v>
-      </c>
-      <c r="E6">
-        <v>0.006</v>
-      </c>
-      <c r="F6">
-        <v>0.006</v>
-      </c>
-      <c r="G6">
-        <v>0.006</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>Building Materials</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Bane 6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C7">
-        <v>0.006</v>
-      </c>
-      <c r="D7">
-        <v>0.006</v>
-      </c>
-      <c r="E7">
-        <v>0.006</v>
-      </c>
-      <c r="F7">
-        <v>0.006</v>
-      </c>
-      <c r="G7">
-        <v>0.006</v>
-      </c>
-      <c r="H7">
-        <v>0.006</v>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Bane 7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C8">
-        <v>0.012</v>
-      </c>
-      <c r="D8">
-        <v>0.006</v>
-      </c>
-      <c r="E8">
-        <v>0.006</v>
-      </c>
-      <c r="F8">
-        <v>0.006</v>
-      </c>
-      <c r="G8">
-        <v>0.006</v>
-      </c>
-      <c r="H8">
-        <v>0.006</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Training Resources</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Bane 8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C9">
-        <v>0.012</v>
-      </c>
-      <c r="D9">
-        <v>0.012</v>
-      </c>
-      <c r="E9">
-        <v>0.006</v>
-      </c>
-      <c r="F9">
-        <v>0.006</v>
-      </c>
-      <c r="G9">
-        <v>0.006</v>
-      </c>
-      <c r="H9">
-        <v>0.006</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Bane 9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C10">
-        <v>0.012</v>
-      </c>
-      <c r="D10">
-        <v>0.012</v>
-      </c>
-      <c r="E10">
-        <v>0.012</v>
-      </c>
-      <c r="F10">
-        <v>0.006</v>
-      </c>
-      <c r="G10">
-        <v>0.006</v>
-      </c>
-      <c r="H10">
-        <v>0.006</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Metal Gathering</v>
-      </c>
-      <c r="J10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Bane 10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C11">
-        <v>0.012</v>
-      </c>
-      <c r="D11">
-        <v>0.012</v>
-      </c>
-      <c r="E11">
-        <v>0.012</v>
-      </c>
-      <c r="F11">
-        <v>0.012</v>
-      </c>
-      <c r="G11">
-        <v>0.006</v>
-      </c>
-      <c r="H11">
-        <v>0.006</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Gas Gathering</v>
-      </c>
-      <c r="J11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Bane Ultra-Enhance</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C12">
-        <v>0.012</v>
-      </c>
-      <c r="D12">
-        <v>0.012</v>
-      </c>
-      <c r="E12">
-        <v>0.012</v>
-      </c>
-      <c r="F12">
-        <v>0.012</v>
-      </c>
-      <c r="G12">
-        <v>0.012</v>
-      </c>
-      <c r="H12">
-        <v>0.006</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Havoc I 1</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13">
-        <v>0.012</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>Infantry Attack</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Havoc I 2</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14">
-        <v>0.012</v>
-      </c>
-      <c r="H14">
-        <v>0.012</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Rider Defense</v>
-      </c>
-      <c r="J14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Havoc I 3</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C15">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15">
-        <v>0.012</v>
-      </c>
-      <c r="H15">
-        <v>0.012</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Hunter Defense</v>
-      </c>
-      <c r="J15">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Havoc I 4</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C16">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D16">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16">
-        <v>0.012</v>
-      </c>
-      <c r="H16">
-        <v>0.012</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Infantry Defense</v>
-      </c>
-      <c r="J16">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Havoc I 5</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C17">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D17">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E17">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17">
-        <v>0.012</v>
-      </c>
-      <c r="H17">
-        <v>0.012</v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Havoc I 6</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C18">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D18">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E18">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F18">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G18">
-        <v>0.012</v>
-      </c>
-      <c r="H18">
-        <v>0.012</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Rider Attack</v>
-      </c>
-      <c r="J18">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Havoc I 7</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C19">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D19">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E19">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F19">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G19">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="H19">
-        <v>0.012</v>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Havoc I 8</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="D20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="H20">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="I20" t="str">
-        <v>Hunter Attack</v>
-      </c>
-      <c r="J20">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Havoc I 9</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C21">
-        <v>0.024</v>
-      </c>
-      <c r="D21">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="E21">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F21">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G21">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="H21">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Havoc I 10</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C22">
-        <v>0.024</v>
-      </c>
-      <c r="D22">
-        <v>0.024</v>
-      </c>
-      <c r="E22">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="F22">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G22">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="H22">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="J22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Havoc I Ultra-Enhance</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C23">
-        <v>0.024</v>
-      </c>
-      <c r="D23">
-        <v>0.024</v>
-      </c>
-      <c r="E23">
-        <v>0.024</v>
-      </c>
-      <c r="F23">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="G23">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="H23">
-        <v>0.018000000000000002</v>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Havoc II 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24">
-        <v>0.024</v>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Havoc II 2</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25">
-        <v>0.024</v>
-      </c>
-      <c r="F25">
-        <v>0.024</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="J25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Havoc II 3</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26">
-        <v>0.024</v>
-      </c>
-      <c r="F26">
-        <v>0.024</v>
-      </c>
-      <c r="G26">
-        <v>0.024</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Havoc II 4</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27">
-        <v>0.024</v>
-      </c>
-      <c r="F27">
-        <v>0.024</v>
-      </c>
-      <c r="G27">
-        <v>0.024</v>
-      </c>
-      <c r="H27">
-        <v>0.024</v>
-      </c>
-      <c r="I27" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="J27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Havoc II 5</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C28">
-        <v>0.03</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28">
-        <v>0.024</v>
-      </c>
-      <c r="F28">
-        <v>0.024</v>
-      </c>
-      <c r="G28">
-        <v>0.024</v>
-      </c>
-      <c r="H28">
-        <v>0.024</v>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Havoc II 6</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C29">
-        <v>0.03</v>
-      </c>
-      <c r="D29">
-        <v>0.03</v>
-      </c>
-      <c r="E29">
-        <v>0.024</v>
-      </c>
-      <c r="F29">
-        <v>0.024</v>
-      </c>
-      <c r="G29">
-        <v>0.024</v>
-      </c>
-      <c r="H29">
-        <v>0.024</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="J29">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Havoc II 7</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C30">
-        <v>0.03</v>
-      </c>
-      <c r="D30">
-        <v>0.03</v>
-      </c>
-      <c r="E30">
-        <v>0.03</v>
-      </c>
-      <c r="F30">
-        <v>0.024</v>
-      </c>
-      <c r="G30">
-        <v>0.024</v>
-      </c>
-      <c r="H30">
-        <v>0.024</v>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Havoc II 8</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C31">
-        <v>0.03</v>
-      </c>
-      <c r="D31">
-        <v>0.03</v>
-      </c>
-      <c r="E31">
-        <v>0.03</v>
-      </c>
-      <c r="F31">
-        <v>0.03</v>
-      </c>
-      <c r="G31">
-        <v>0.024</v>
-      </c>
-      <c r="H31">
-        <v>0.024</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="J31">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Havoc II 9</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C32">
-        <v>0.03</v>
-      </c>
-      <c r="D32">
-        <v>0.03</v>
-      </c>
-      <c r="E32">
-        <v>0.03</v>
-      </c>
-      <c r="F32">
-        <v>0.03</v>
-      </c>
-      <c r="G32">
-        <v>0.03</v>
-      </c>
-      <c r="H32">
-        <v>0.024</v>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Havoc II 10</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C33">
-        <v>0.03</v>
-      </c>
-      <c r="D33">
-        <v>0.03</v>
-      </c>
-      <c r="E33">
-        <v>0.03</v>
-      </c>
-      <c r="F33">
-        <v>0.03</v>
-      </c>
-      <c r="G33">
-        <v>0.03</v>
-      </c>
-      <c r="H33">
-        <v>0.03</v>
-      </c>
-      <c r="I33" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="J33">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Havoc II Ultra-Enhance</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C34">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D34">
-        <v>0.03</v>
-      </c>
-      <c r="E34">
-        <v>0.03</v>
-      </c>
-      <c r="F34">
-        <v>0.03</v>
-      </c>
-      <c r="G34">
-        <v>0.03</v>
-      </c>
-      <c r="H34">
-        <v>0.03</v>
-      </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-      <c r="J34">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Scourge I 1</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C35">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v>Active Strike</v>
-      </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Scourge I 2</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C36">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D36">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="J36">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Scourge I 3</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C37">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D37">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E37">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="J37">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Scourge I 4</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C38">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D38">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E38">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F38">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v>Troop Attack</v>
-      </c>
-      <c r="J38">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Scourge I 5</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C39">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D39">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E39">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F39">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G39">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Scourge I 6</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="D40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H40">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-      <c r="J40">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Scourge I 7</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C41">
-        <v>0.042</v>
-      </c>
-      <c r="D41">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="E41">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F41">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G41">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H41">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I41" t="str">
-        <v>Rally Attack</v>
-      </c>
-      <c r="J41">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Scourge I 8</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C42">
-        <v>0.042</v>
-      </c>
-      <c r="D42">
-        <v>0.042</v>
-      </c>
-      <c r="E42">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="F42">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G42">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H42">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Scourge I 9</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C43">
-        <v>0.042</v>
-      </c>
-      <c r="D43">
-        <v>0.042</v>
-      </c>
-      <c r="E43">
-        <v>0.042</v>
-      </c>
-      <c r="F43">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="G43">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H43">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Scourge I 10</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C44">
-        <v>0.042</v>
-      </c>
-      <c r="D44">
-        <v>0.042</v>
-      </c>
-      <c r="E44">
-        <v>0.042</v>
-      </c>
-      <c r="F44">
-        <v>0.042</v>
-      </c>
-      <c r="G44">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="H44">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I44" t="str">
-        <v>Troop Lethality</v>
-      </c>
-      <c r="J44">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Scourge I Ultra-Enhance</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C45">
-        <v>0.042</v>
-      </c>
-      <c r="D45">
-        <v>0.042</v>
-      </c>
-      <c r="E45">
-        <v>0.042</v>
-      </c>
-      <c r="F45">
-        <v>0.042</v>
-      </c>
-      <c r="G45">
-        <v>0.042</v>
-      </c>
-      <c r="H45">
-        <v>0.036000000000000004</v>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="J45">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Scourge II 1</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46">
-        <v>0.042</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-      <c r="J46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Scourge II 2</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="D47" t="str">
-        <v/>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47">
-        <v>0.042</v>
-      </c>
-      <c r="H47">
-        <v>0.042</v>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-      <c r="J47">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Scourge II 3</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C48">
-        <v>0.048</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48">
-        <v>0.042</v>
-      </c>
-      <c r="H48">
-        <v>0.042</v>
-      </c>
-      <c r="I48" t="str">
-        <v>Rally Lethality</v>
-      </c>
-      <c r="J48">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Scourge II 4</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C49">
-        <v>0.048</v>
-      </c>
-      <c r="D49">
-        <v>0.048</v>
-      </c>
-      <c r="E49" t="str">
-        <v/>
-      </c>
-      <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49">
-        <v>0.042</v>
-      </c>
-      <c r="H49">
-        <v>0.042</v>
-      </c>
-      <c r="I49" t="str">
-        <v/>
-      </c>
-      <c r="J49">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Scourge II 5</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C50">
-        <v>0.048</v>
-      </c>
-      <c r="D50">
-        <v>0.048</v>
-      </c>
-      <c r="E50">
-        <v>0.048</v>
-      </c>
-      <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50">
-        <v>0.042</v>
-      </c>
-      <c r="H50">
-        <v>0.042</v>
-      </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="J50">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Scourge II 6</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C51">
-        <v>0.048</v>
-      </c>
-      <c r="D51">
-        <v>0.048</v>
-      </c>
-      <c r="E51">
-        <v>0.048</v>
-      </c>
-      <c r="F51">
-        <v>0.048</v>
-      </c>
-      <c r="G51">
-        <v>0.042</v>
-      </c>
-      <c r="H51">
-        <v>0.042</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Troop Defense</v>
-      </c>
-      <c r="J51">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Scourge II 7</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C52">
-        <v>0.048</v>
-      </c>
-      <c r="D52">
-        <v>0.048</v>
-      </c>
-      <c r="E52">
-        <v>0.048</v>
-      </c>
-      <c r="F52">
-        <v>0.048</v>
-      </c>
-      <c r="G52">
-        <v>0.048</v>
-      </c>
-      <c r="H52">
-        <v>0.042</v>
-      </c>
-      <c r="I52" t="str">
-        <v/>
-      </c>
-      <c r="J52">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Scourge II 8</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C53">
-        <v>0.048</v>
-      </c>
-      <c r="D53">
-        <v>0.048</v>
-      </c>
-      <c r="E53">
-        <v>0.048</v>
-      </c>
-      <c r="F53">
-        <v>0.048</v>
-      </c>
-      <c r="G53">
-        <v>0.048</v>
-      </c>
-      <c r="H53">
-        <v>0.048</v>
-      </c>
-      <c r="I53" t="str">
-        <v/>
-      </c>
-      <c r="J53">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Scourge II 9</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C54">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="D54">
-        <v>0.048</v>
-      </c>
-      <c r="E54">
-        <v>0.048</v>
-      </c>
-      <c r="F54">
-        <v>0.048</v>
-      </c>
-      <c r="G54">
-        <v>0.048</v>
-      </c>
-      <c r="H54">
-        <v>0.048</v>
-      </c>
-      <c r="I54" t="str">
-        <v>Rally Defense</v>
-      </c>
-      <c r="J54">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Scourge II 10</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C55">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="D55">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="E55">
-        <v>0.048</v>
-      </c>
-      <c r="F55">
-        <v>0.048</v>
-      </c>
-      <c r="G55">
-        <v>0.048</v>
-      </c>
-      <c r="H55">
-        <v>0.048</v>
-      </c>
-      <c r="I55" t="str">
-        <v/>
-      </c>
-      <c r="J55">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Scourge II Ultra-Enhance</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C56">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="D56">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="E56">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F56">
-        <v>0.048</v>
-      </c>
-      <c r="G56">
-        <v>0.048</v>
-      </c>
-      <c r="H56">
-        <v>0.048</v>
-      </c>
-      <c r="I56" t="str">
-        <v/>
-      </c>
-      <c r="J56">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Scourge III 1</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
-      <c r="J57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Scourge III 2</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F58">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G58" t="str">
-        <v/>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v>Troop Health</v>
-      </c>
-      <c r="J58">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Scourge III 3</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F59">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G59">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Scourge III 4</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F60">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G60">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H60">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-      <c r="J60">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Scourge III 5</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Infantry Lethality</v>
-      </c>
-      <c r="C61">
-        <v>0.06</v>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F61">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G61">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H61">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I61" t="str">
-        <v>Rally Health</v>
-      </c>
-      <c r="J61">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Scourge III 6</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Infantry Health</v>
-      </c>
-      <c r="C62">
-        <v>0.06</v>
-      </c>
-      <c r="D62">
-        <v>0.06</v>
-      </c>
-      <c r="E62">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="F62">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G62">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H62">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I62" t="str">
-        <v/>
-      </c>
-      <c r="J62">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Scourge III 7</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Rider Lethality</v>
-      </c>
-      <c r="C63">
-        <v>0.06</v>
-      </c>
-      <c r="D63">
-        <v>0.06</v>
-      </c>
-      <c r="E63">
-        <v>0.06</v>
-      </c>
-      <c r="F63">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="G63">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H63">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I63" t="str">
-        <v>March Capacity</v>
-      </c>
-      <c r="J63">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Scourge III 8</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Rider Health</v>
-      </c>
-      <c r="C64">
-        <v>0.06</v>
-      </c>
-      <c r="D64">
-        <v>0.06</v>
-      </c>
-      <c r="E64">
-        <v>0.06</v>
-      </c>
-      <c r="F64">
-        <v>0.06</v>
-      </c>
-      <c r="G64">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="H64">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="J64">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Scourge III 9</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Hunter Lethality</v>
-      </c>
-      <c r="C65">
-        <v>0.06</v>
-      </c>
-      <c r="D65">
-        <v>0.06</v>
-      </c>
-      <c r="E65">
-        <v>0.06</v>
-      </c>
-      <c r="F65">
-        <v>0.06</v>
-      </c>
-      <c r="G65">
-        <v>0.06</v>
-      </c>
-      <c r="H65">
-        <v>0.054000000000000006</v>
-      </c>
-      <c r="I65" t="str">
-        <v>Rally Capacity</v>
-      </c>
-      <c r="J65">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Scourge III 10</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Hunter Health</v>
-      </c>
-      <c r="C66">
-        <v>0.06</v>
-      </c>
-      <c r="D66">
-        <v>0.06</v>
-      </c>
-      <c r="E66">
-        <v>0.06</v>
-      </c>
-      <c r="F66">
-        <v>0.06</v>
-      </c>
-      <c r="G66">
-        <v>0.06</v>
-      </c>
-      <c r="H66">
-        <v>0.06</v>
-      </c>
-      <c r="I66" t="str">
-        <v>Adapt &amp; Overcome</v>
-      </c>
-      <c r="J66">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
+++ b/src/data/excel/Behemoth_Enhancements_FINAL.xlsx
@@ -7,8 +7,8 @@
     <sheet name="MK IV" sheetId="2" r:id="rId2"/>
     <sheet name="MK V" sheetId="3" r:id="rId3"/>
     <sheet name="MK 0" sheetId="4" r:id="rId4"/>
-    <sheet name="MK I" sheetId="5" r:id="rId5"/>
-    <sheet name="MK II" sheetId="6" r:id="rId6"/>
+    <sheet name="MK II" sheetId="5" r:id="rId5"/>
+    <sheet name="MK I" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -10214,10 +10214,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>Artillery Barrage</v>
-      </c>
-      <c r="J2">
-        <v>2230</v>
+        <v>Wild Shot</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -10249,7 +10249,7 @@
         <v/>
       </c>
       <c r="J3">
-        <v>894</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -10278,10 +10278,10 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>Rapid Fire</v>
+        <v>Ammo Refill</v>
       </c>
       <c r="J4">
-        <v>3968</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -10313,7 +10313,7 @@
         <v/>
       </c>
       <c r="J5">
-        <v>4849</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -10345,7 +10345,7 @@
         <v/>
       </c>
       <c r="J6">
-        <v>5709</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -10374,10 +10374,10 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>Suppressive Barrage</v>
+        <v>Precise Suppression</v>
       </c>
       <c r="J7">
-        <v>6569</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -10409,7 +10409,7 @@
         <v/>
       </c>
       <c r="J8">
-        <v>7449</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -10441,7 +10441,7 @@
         <v/>
       </c>
       <c r="J9">
-        <v>8360</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -10473,7 +10473,7 @@
         <v/>
       </c>
       <c r="J10">
-        <v>9221</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="J11">
-        <v>10103</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -10537,7 +10537,7 @@
         <v/>
       </c>
       <c r="J12">
-        <v>10962</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -10566,10 +10566,10 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>Destructive Missile</v>
-      </c>
-      <c r="J13">
-        <v>10940</v>
+        <v>Iron Shield</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -10601,7 +10601,7 @@
         <v/>
       </c>
       <c r="J14">
-        <v>11815</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -10630,10 +10630,10 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>Infantry Recharge</v>
+        <v>Beast of Steel I</v>
       </c>
       <c r="J15">
-        <v>12685</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -10665,7 +10665,7 @@
         <v/>
       </c>
       <c r="J16">
-        <v>13565</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="J17">
-        <v>14455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -10726,10 +10726,10 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>Rider Recharge</v>
+        <v>Beast of Steel II</v>
       </c>
       <c r="J18">
-        <v>15335</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -10761,7 +10761,7 @@
         <v/>
       </c>
       <c r="J19">
-        <v>16106</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -10793,7 +10793,7 @@
         <v/>
       </c>
       <c r="J20">
-        <v>16996</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -10822,10 +10822,10 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>Hunter Recharge</v>
+        <v>Beast of Steel III</v>
       </c>
       <c r="J21">
-        <v>17877</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -10857,7 +10857,7 @@
         <v/>
       </c>
       <c r="J22">
-        <v>18767</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -10886,10 +10886,10 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>Quick Recharge</v>
+        <v>Instant Cooldown</v>
       </c>
       <c r="J23">
-        <v>19148</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -10920,8 +10920,8 @@
       <c r="I24" t="str">
         <v/>
       </c>
-      <c r="J24">
-        <v>19130</v>
+      <c r="J24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -10953,7 +10953,7 @@
         <v/>
       </c>
       <c r="J25">
-        <v>19648</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -10982,10 +10982,10 @@
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>Target: Infantry</v>
+        <v>Divine Shield I</v>
       </c>
       <c r="J26">
-        <v>20028</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -11017,7 +11017,7 @@
         <v/>
       </c>
       <c r="J27">
-        <v>20529</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -11046,10 +11046,10 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>Target: Riders</v>
+        <v>Divine Shield II</v>
       </c>
       <c r="J28">
-        <v>20919</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -11081,7 +11081,7 @@
         <v/>
       </c>
       <c r="J29">
-        <v>21309</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -11110,10 +11110,10 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>Target: Hunters</v>
+        <v>Divine Shield III</v>
       </c>
       <c r="J30">
-        <v>21799</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -11142,10 +11142,10 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Genetic Reconstruction</v>
       </c>
       <c r="J31">
-        <v>22190</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -11174,10 +11174,10 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>Core Destruction</v>
+        <v/>
       </c>
       <c r="J32">
-        <v>22690</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -11209,7 +11209,7 @@
         <v/>
       </c>
       <c r="J33">
-        <v>23081</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -11241,7 +11241,7 @@
         <v/>
       </c>
       <c r="J34">
-        <v>23475</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -11270,10 +11270,10 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>Electromagnetic Protection</v>
-      </c>
-      <c r="J35">
-        <v>23440</v>
+        <v>Rain of Bullets</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -11305,7 +11305,7 @@
         <v/>
       </c>
       <c r="J36">
-        <v>23963</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -11337,7 +11337,7 @@
         <v/>
       </c>
       <c r="J37">
-        <v>24343</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
@@ -11366,10 +11366,10 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>Infantry Induction</v>
+        <v>Energy Resonance I</v>
       </c>
       <c r="J38">
-        <v>24844</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -11401,7 +11401,7 @@
         <v/>
       </c>
       <c r="J39">
-        <v>25234</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
@@ -11433,7 +11433,7 @@
         <v/>
       </c>
       <c r="J40">
-        <v>25733</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
@@ -11465,7 +11465,7 @@
         <v/>
       </c>
       <c r="J41">
-        <v>26115</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
@@ -11494,10 +11494,10 @@
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>Rider Induction</v>
+        <v>Energy Resonance II</v>
       </c>
       <c r="J42">
-        <v>26615</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -11529,7 +11529,7 @@
         <v/>
       </c>
       <c r="J43">
-        <v>27006</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
@@ -11561,7 +11561,7 @@
         <v/>
       </c>
       <c r="J44">
-        <v>27397</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -11590,10 +11590,10 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>Hunter Induction</v>
+        <v>Energy Resonance III</v>
       </c>
       <c r="J45">
-        <v>27768</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -11624,8 +11624,8 @@
       <c r="I46" t="str">
         <v/>
       </c>
-      <c r="J46">
-        <v>27740</v>
+      <c r="J46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -11657,7 +11657,7 @@
         <v/>
       </c>
       <c r="J47">
-        <v>28158</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -11689,7 +11689,7 @@
         <v/>
       </c>
       <c r="J48">
-        <v>28539</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -11718,10 +11718,10 @@
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>High Voltage</v>
+        <v>Full Blast</v>
       </c>
       <c r="J49">
-        <v>29029</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="J50">
-        <v>29409</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -11785,7 +11785,7 @@
         <v/>
       </c>
       <c r="J51">
-        <v>29789</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
@@ -11817,7 +11817,7 @@
         <v/>
       </c>
       <c r="J52">
-        <v>30180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -11846,10 +11846,10 @@
         <v/>
       </c>
       <c r="I53" t="str">
-        <v>Infantry Protection</v>
+        <v>Toxin Spread I</v>
       </c>
       <c r="J53">
-        <v>30550</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -11881,7 +11881,7 @@
         <v/>
       </c>
       <c r="J54">
-        <v>30941</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
@@ -11913,7 +11913,7 @@
         <v/>
       </c>
       <c r="J55">
-        <v>31322</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
@@ -11942,10 +11942,10 @@
         <v/>
       </c>
       <c r="I56" t="str">
-        <v>Rider Protection</v>
+        <v>Toxin Spread II</v>
       </c>
       <c r="J56">
-        <v>31705</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -11976,8 +11976,8 @@
       <c r="I57" t="str">
         <v/>
       </c>
-      <c r="J57">
-        <v>31670</v>
+      <c r="J57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -12009,7 +12009,7 @@
         <v/>
       </c>
       <c r="J58">
-        <v>32087</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
@@ -12041,7 +12041,7 @@
         <v/>
       </c>
       <c r="J59">
-        <v>32469</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
@@ -12070,10 +12070,10 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>Hunter Protection</v>
+        <v>Toxin Spread III</v>
       </c>
       <c r="J60">
-        <v>32971</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -12105,7 +12105,7 @@
         <v/>
       </c>
       <c r="J61">
-        <v>33234</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
@@ -12137,7 +12137,7 @@
         <v/>
       </c>
       <c r="J62">
-        <v>33738</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -12169,7 +12169,7 @@
         <v/>
       </c>
       <c r="J63">
-        <v>34122</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
@@ -12198,10 +12198,10 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>Core Reinforcement</v>
+        <v>Energy Fusion</v>
       </c>
       <c r="J64">
-        <v>34507</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
@@ -12233,7 +12233,7 @@
         <v/>
       </c>
       <c r="J65">
-        <v>34893</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
@@ -12265,7 +12265,7 @@
         <v/>
       </c>
       <c r="J66">
-        <v>35286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -12297,7 +12297,7 @@
         <v/>
       </c>
       <c r="J67">
-        <v>35610</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68">
@@ -12326,10 +12326,10 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v>Dominating Aura</v>
-      </c>
-      <c r="J68">
-        <v>35460</v>
+        <v>Life Absorption</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -12361,7 +12361,7 @@
         <v/>
       </c>
       <c r="J69">
-        <v>35680</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
@@ -12390,10 +12390,10 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>Hunting Aura</v>
+        <v>Blood Conversion I</v>
       </c>
       <c r="J70">
-        <v>35930</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71">
@@ -12425,7 +12425,7 @@
         <v/>
       </c>
       <c r="J71">
-        <v>36181</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
@@ -12457,7 +12457,7 @@
         <v/>
       </c>
       <c r="J72">
-        <v>36432</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
@@ -12486,10 +12486,10 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v>Charging Aura</v>
+        <v>Blood Conversion II</v>
       </c>
       <c r="J73">
-        <v>36563</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
@@ -12521,7 +12521,7 @@
         <v/>
       </c>
       <c r="J74">
-        <v>36814</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75">
@@ -12553,7 +12553,7 @@
         <v/>
       </c>
       <c r="J75">
-        <v>37065</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76">
@@ -12582,10 +12582,10 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>Shooting Aura</v>
+        <v>Blood Conversion III</v>
       </c>
       <c r="J76">
-        <v>37207</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="J77">
-        <v>37451</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78">
@@ -12646,10 +12646,10 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>Piercing Aura</v>
+        <v>EM Interference</v>
       </c>
       <c r="J78">
-        <v>37706</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -12680,8 +12680,8 @@
       <c r="I79" t="str">
         <v/>
       </c>
-      <c r="J79">
-        <v>37610</v>
+      <c r="J79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -12713,7 +12713,7 @@
         <v/>
       </c>
       <c r="J80">
-        <v>37846</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81">
@@ -12742,10 +12742,10 @@
         <v/>
       </c>
       <c r="I81" t="str">
-        <v>Rapid Concentration</v>
+        <v>Gene Optimization</v>
       </c>
       <c r="J81">
-        <v>38097</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82">
@@ -12777,7 +12777,7 @@
         <v/>
       </c>
       <c r="J82">
-        <v>38348</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83">
@@ -12809,7 +12809,7 @@
         <v/>
       </c>
       <c r="J83">
-        <v>38489</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84">
@@ -12838,10 +12838,10 @@
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>Buffer Aura</v>
+        <v>Energy Transfer I</v>
       </c>
       <c r="J84">
-        <v>38740</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -12873,7 +12873,7 @@
         <v/>
       </c>
       <c r="J85">
-        <v>38991</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86">
@@ -12905,7 +12905,7 @@
         <v/>
       </c>
       <c r="J86">
-        <v>39233</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87">
@@ -12934,10 +12934,10 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v>Cover Aura</v>
+        <v>Energy Transfer II</v>
       </c>
       <c r="J87">
-        <v>39375</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88">
@@ -12969,7 +12969,7 @@
         <v/>
       </c>
       <c r="J88">
-        <v>39630</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89">
@@ -12998,10 +12998,10 @@
         <v/>
       </c>
       <c r="I89" t="str">
-        <v>Protection Aura</v>
+        <v>Energy Transfer III</v>
       </c>
       <c r="J89">
-        <v>39890</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90">
@@ -13032,8 +13032,8 @@
       <c r="I90" t="str">
         <v/>
       </c>
-      <c r="J90">
-        <v>39770</v>
+      <c r="J90" t="str">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -13065,7 +13065,7 @@
         <v/>
       </c>
       <c r="J91">
-        <v>40025</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92">
@@ -13097,7 +13097,7 @@
         <v/>
       </c>
       <c r="J92">
-        <v>40281</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93">
@@ -13126,10 +13126,10 @@
         <v/>
       </c>
       <c r="I93" t="str">
-        <v>Precise Reinforcement</v>
+        <v>Induction Barrier</v>
       </c>
       <c r="J93">
-        <v>40419</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94">
@@ -13161,7 +13161,7 @@
         <v/>
       </c>
       <c r="J94">
-        <v>40678</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95">
@@ -13193,7 +13193,7 @@
         <v/>
       </c>
       <c r="J95">
-        <v>40829</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96">
@@ -13225,7 +13225,7 @@
         <v/>
       </c>
       <c r="J96">
-        <v>41083</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97">
@@ -13254,10 +13254,10 @@
         <v/>
       </c>
       <c r="I97" t="str">
-        <v>Corrosion Aura</v>
+        <v>Life Devour</v>
       </c>
       <c r="J97">
-        <v>41239</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98">
@@ -13289,7 +13289,7 @@
         <v/>
       </c>
       <c r="J98">
-        <v>41498</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99">
@@ -13321,7 +13321,7 @@
         <v/>
       </c>
       <c r="J99">
-        <v>41790</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100">
@@ -13353,7 +13353,7 @@
         <v/>
       </c>
       <c r="J100">
-        <v>42190</v>
+        <v>520</v>
       </c>
     </row>
     <row r="101">
@@ -13384,8 +13384,8 @@
       <c r="I101" t="str">
         <v/>
       </c>
-      <c r="J101">
-        <v>41670</v>
+      <c r="J101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -13414,10 +13414,10 @@
         <v/>
       </c>
       <c r="I102" t="str">
-        <v>Destructive Ray</v>
+        <v>Flame Eruption</v>
       </c>
       <c r="J102">
-        <v>42072</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103">
@@ -13446,10 +13446,10 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>Infantry Concentration</v>
+        <v>Flame Sublimation I</v>
       </c>
       <c r="J103">
-        <v>42323</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104">
@@ -13481,7 +13481,7 @@
         <v/>
       </c>
       <c r="J104">
-        <v>42564</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105">
@@ -13513,7 +13513,7 @@
         <v/>
       </c>
       <c r="J105">
-        <v>42706</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106">
@@ -13542,10 +13542,10 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>Rider Concentration</v>
+        <v>Flame Sublimation II</v>
       </c>
       <c r="J106">
-        <v>42948</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107">
@@ -13577,7 +13577,7 @@
         <v/>
       </c>
       <c r="J107">
-        <v>43091</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108">
@@ -13609,7 +13609,7 @@
         <v/>
       </c>
       <c r="J108">
-        <v>43334</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109">
@@ -13638,10 +13638,10 @@
         <v/>
       </c>
       <c r="I109" t="str">
-        <v>Hunter Concentration</v>
+        <v>Flame Sublimation III</v>
       </c>
       <c r="J109">
-        <v>43479</v>
+        <v>279</v>
       </c>
     </row>
     <row r="110">
@@ -13673,7 +13673,7 @@
         <v/>
       </c>
       <c r="J110">
-        <v>43726</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111">
@@ -13702,10 +13702,10 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v>Deep Burn</v>
+        <v>Rejuvenate</v>
       </c>
       <c r="J111">
-        <v>43872</v>
+        <v>302</v>
       </c>
     </row>
     <row r="112">
@@ -13736,8 +13736,8 @@
       <c r="I112" t="str">
         <v/>
       </c>
-      <c r="J112">
-        <v>43570</v>
+      <c r="J112" t="str">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -13769,7 +13769,7 @@
         <v/>
       </c>
       <c r="J113">
-        <v>43993</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114">
@@ -13798,10 +13798,10 @@
         <v/>
       </c>
       <c r="I114" t="str">
-        <v>Energy Reserves</v>
+        <v>Energy Optimization</v>
       </c>
       <c r="J114">
-        <v>44124</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115">
@@ -13833,7 +13833,7 @@
         <v/>
       </c>
       <c r="J115">
-        <v>44191</v>
+        <v>306</v>
       </c>
     </row>
     <row r="116">
@@ -13865,7 +13865,7 @@
         <v/>
       </c>
       <c r="J116">
-        <v>44258</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117">
@@ -13894,10 +13894,10 @@
         <v/>
       </c>
       <c r="I117" t="str">
-        <v>Infantry Block</v>
+        <v>Blaze Barrier I</v>
       </c>
       <c r="J117">
-        <v>44390</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118">
@@ -13929,7 +13929,7 @@
         <v/>
       </c>
       <c r="J118">
-        <v>44513</v>
+        <v>313</v>
       </c>
     </row>
     <row r="119">
@@ -13961,7 +13961,7 @@
         <v/>
       </c>
       <c r="J119">
-        <v>44647</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120">
@@ -13990,10 +13990,10 @@
         <v/>
       </c>
       <c r="I120" t="str">
-        <v>Rider Block</v>
+        <v>Blaze Barrier II</v>
       </c>
       <c r="J120">
-        <v>44772</v>
+        <v>322</v>
       </c>
     </row>
     <row r="121">
@@ -14025,7 +14025,7 @@
         <v/>
       </c>
       <c r="J121">
-        <v>44856</v>
+        <v>331</v>
       </c>
     </row>
     <row r="122">
@@ -14057,7 +14057,7 @@
         <v/>
       </c>
       <c r="J122">
-        <v>44938</v>
+        <v>348</v>
       </c>
     </row>
     <row r="123">
@@ -14086,10 +14086,10 @@
         <v/>
       </c>
       <c r="I123" t="str">
-        <v/>
-      </c>
-      <c r="J123">
-        <v>44590</v>
+        <v>Blaze Barrier III</v>
+      </c>
+      <c r="J123" t="str">
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -14121,7 +14121,7 @@
         <v/>
       </c>
       <c r="J124">
-        <v>45070</v>
+        <v>350</v>
       </c>
     </row>
     <row r="125">
@@ -14153,7 +14153,7 @@
         <v/>
       </c>
       <c r="J125">
-        <v>45191</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126">
@@ -14182,10 +14182,10 @@
         <v/>
       </c>
       <c r="I126" t="str">
-        <v>Thermal Insulation</v>
+        <v>Fire of Life</v>
       </c>
       <c r="J126">
-        <v>45323</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127">
@@ -14217,7 +14217,7 @@
         <v/>
       </c>
       <c r="J127">
-        <v>45445</v>
+        <v>355</v>
       </c>
     </row>
     <row r="128">
@@ -14249,7 +14249,7 @@
         <v/>
       </c>
       <c r="J128">
-        <v>45513</v>
+        <v>358</v>
       </c>
     </row>
     <row r="129">
@@ -14281,7 +14281,7 @@
         <v/>
       </c>
       <c r="J129">
-        <v>45592</v>
+        <v>362</v>
       </c>
     </row>
     <row r="130">
@@ -14313,7 +14313,7 @@
         <v/>
       </c>
       <c r="J130">
-        <v>45716</v>
+        <v>366</v>
       </c>
     </row>
     <row r="131">
@@ -14345,7 +14345,7 @@
         <v/>
       </c>
       <c r="J131">
-        <v>45852</v>
+        <v>372</v>
       </c>
     </row>
     <row r="132">
@@ -14374,10 +14374,10 @@
         <v/>
       </c>
       <c r="I132" t="str">
-        <v>Ray Dilution</v>
+        <v>Flame Absorption</v>
       </c>
       <c r="J132">
-        <v>45978</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -14389,7 +14389,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J132"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -14435,9 +14435,4201 @@
         <v>Fragments Required</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Bane 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>Artillery Barrage</v>
+      </c>
+      <c r="J2">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Bane 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Bane 3</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Rapid Fire</v>
+      </c>
+      <c r="J4">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Bane 4</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5">
+        <v>4849</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Bane 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6">
+        <v>5709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Bane 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Suppressive Barrage</v>
+      </c>
+      <c r="J7">
+        <v>6569</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bane 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
+        <v>7449</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Bane 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
+        <v>8360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Bane 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10">
+        <v>9221</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Bane 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11">
+        <v>10103</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Bane Ultra-Enhance</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>10962</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Havoc I 1</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Destructive Missile</v>
+      </c>
+      <c r="J13">
+        <v>10940</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Havoc I 2</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
+        <v>11815</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Havoc I 3</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Infantry Recharge</v>
+      </c>
+      <c r="J15">
+        <v>12685</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Havoc I 4</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16">
+        <v>13565</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Havoc I 5</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
+        <v>14455</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Havoc I 6</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Rider Recharge</v>
+      </c>
+      <c r="J18">
+        <v>15335</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Havoc I 7</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19">
+        <v>16106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Havoc I 8</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20">
+        <v>16996</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Havoc I 9</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Hunter Recharge</v>
+      </c>
+      <c r="J21">
+        <v>17877</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Havoc I 10</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22">
+        <v>18767</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Havoc I Ultra-Enhance</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Quick Recharge</v>
+      </c>
+      <c r="J23">
+        <v>19148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Havoc II 1</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24">
+        <v>19130</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Havoc II 2</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25">
+        <v>19648</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Havoc II 3</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Target: Infantry</v>
+      </c>
+      <c r="J26">
+        <v>20028</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Havoc II 4</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27">
+        <v>20529</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Havoc II 5</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Target: Riders</v>
+      </c>
+      <c r="J28">
+        <v>20919</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Havoc II 6</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29">
+        <v>21309</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Havoc II 7</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Target: Hunters</v>
+      </c>
+      <c r="J30">
+        <v>21799</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Havoc II 8</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31">
+        <v>22190</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Havoc II 9</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Core Destruction</v>
+      </c>
+      <c r="J32">
+        <v>22690</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Havoc II 10</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33">
+        <v>23081</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Havoc II Ultra-Enhance</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34">
+        <v>23475</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Scourge I 1</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Electromagnetic Protection</v>
+      </c>
+      <c r="J35">
+        <v>23440</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Scourge I 2</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36">
+        <v>23963</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Scourge I 3</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37">
+        <v>24343</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Scourge I 4</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Infantry Induction</v>
+      </c>
+      <c r="J38">
+        <v>24844</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Scourge I 5</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39">
+        <v>25234</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Scourge I 6</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40">
+        <v>25733</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Scourge I 7</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41">
+        <v>26115</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Scourge I 8</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>Rider Induction</v>
+      </c>
+      <c r="J42">
+        <v>26615</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Scourge I 9</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43">
+        <v>27006</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Scourge I 10</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44">
+        <v>27397</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Scourge I Ultra-Enhance</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>Hunter Induction</v>
+      </c>
+      <c r="J45">
+        <v>27768</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Scourge II 1</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46">
+        <v>27740</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Scourge II 2</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47">
+        <v>28158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Scourge II 3</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48">
+        <v>28539</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Scourge II 4</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>High Voltage</v>
+      </c>
+      <c r="J49">
+        <v>29029</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Scourge II 5</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50">
+        <v>29409</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Scourge II 6</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51">
+        <v>29789</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Scourge II 7</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52">
+        <v>30180</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Scourge II 8</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Infantry Protection</v>
+      </c>
+      <c r="J53">
+        <v>30550</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Scourge II 9</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54">
+        <v>30941</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Scourge II 10</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55">
+        <v>31322</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Scourge II Ultra-Enhance</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>Rider Protection</v>
+      </c>
+      <c r="J56">
+        <v>31705</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Scourge III 1</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57">
+        <v>31670</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Scourge III 2</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58">
+        <v>32087</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Scourge III 3</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59">
+        <v>32469</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Scourge III 4</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>Hunter Protection</v>
+      </c>
+      <c r="J60">
+        <v>32971</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Scourge III 5</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Scourge III 6</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62">
+        <v>33738</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Scourge III 7</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63">
+        <v>34122</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Scourge III 8</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>Core Reinforcement</v>
+      </c>
+      <c r="J64">
+        <v>34507</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Scourge III 9</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65">
+        <v>34893</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Scourge III 10</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66">
+        <v>35286</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Scourge III Ultra-Enhance</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67">
+        <v>35610</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Cataclysm I 1</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v>Dominating Aura</v>
+      </c>
+      <c r="J68">
+        <v>35460</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Cataclysm I 2</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69">
+        <v>35680</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Cataclysm I 3</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v>Hunting Aura</v>
+      </c>
+      <c r="J70">
+        <v>35930</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Cataclysm I 4</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71">
+        <v>36181</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Cataclysm I 5</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72">
+        <v>36432</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Cataclysm I 6</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v>Charging Aura</v>
+      </c>
+      <c r="J73">
+        <v>36563</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Cataclysm I 7</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74">
+        <v>36814</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Cataclysm I 8</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75">
+        <v>37065</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Cataclysm I 9</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v>Shooting Aura</v>
+      </c>
+      <c r="J76">
+        <v>37207</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Cataclysm I 10</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77">
+        <v>37451</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Cataclysm I Ultra-Enhance</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v>Piercing Aura</v>
+      </c>
+      <c r="J78">
+        <v>37706</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Cataclysm II 1</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79">
+        <v>37610</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Cataclysm II 2</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80">
+        <v>37846</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Cataclysm II 3</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v>Rapid Concentration</v>
+      </c>
+      <c r="J81">
+        <v>38097</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Cataclysm II 4</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82">
+        <v>38348</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Cataclysm II 5</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83">
+        <v>38489</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Cataclysm II 6</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v>Buffer Aura</v>
+      </c>
+      <c r="J84">
+        <v>38740</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Cataclysm II 7</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85">
+        <v>38991</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Cataclysm II 8</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86">
+        <v>39233</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Cataclysm II 9</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v>Cover Aura</v>
+      </c>
+      <c r="J87">
+        <v>39375</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Cataclysm II 10</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88">
+        <v>39630</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Cataclysm II Ultra-Enhance</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v>Protection Aura</v>
+      </c>
+      <c r="J89">
+        <v>39890</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Cataclysm III 1</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90">
+        <v>39770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Cataclysm III 2</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91">
+        <v>40025</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Cataclysm III 3</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92">
+        <v>40281</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Cataclysm III 4</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v>Precise Reinforcement</v>
+      </c>
+      <c r="J93">
+        <v>40419</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Cataclysm III 5</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94">
+        <v>40678</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Cataclysm III 6</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95">
+        <v>40829</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Cataclysm III 7</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96">
+        <v>41083</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Cataclysm III 8</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>Corrosion Aura</v>
+      </c>
+      <c r="J97">
+        <v>41239</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Cataclysm III 9</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98">
+        <v>41498</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Cataclysm III 10</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99">
+        <v>41790</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Cataclysm III Ultra-Enhance</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100">
+        <v>42190</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Abaddon I 1</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101">
+        <v>41670</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Abaddon I 2</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v>Destructive Ray</v>
+      </c>
+      <c r="J102">
+        <v>42072</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Abaddon I 3</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v>Infantry Concentration</v>
+      </c>
+      <c r="J103">
+        <v>42323</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Abaddon I 4</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104">
+        <v>42564</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Abaddon I 5</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105">
+        <v>42706</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Abaddon I 6</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v>Rider Concentration</v>
+      </c>
+      <c r="J106">
+        <v>42948</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Abaddon I 7</v>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107">
+        <v>43091</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Abaddon I 8</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108">
+        <v>43334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Abaddon I 9</v>
+      </c>
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v>Hunter Concentration</v>
+      </c>
+      <c r="J109">
+        <v>43479</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Abaddon I 10</v>
+      </c>
+      <c r="B110" t="str">
+        <v/>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110">
+        <v>43726</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Abaddon I Ultra-Enhance</v>
+      </c>
+      <c r="B111" t="str">
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v>Deep Burn</v>
+      </c>
+      <c r="J111">
+        <v>43872</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Abaddon II 1</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112">
+        <v>43570</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Abaddon II 2</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113">
+        <v>43993</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Abaddon II 3</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v>Energy Reserves</v>
+      </c>
+      <c r="J114">
+        <v>44124</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Abaddon II 4</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115">
+        <v>44191</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Abaddon II 5</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116">
+        <v>44258</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Abaddon II 6</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>Infantry Block</v>
+      </c>
+      <c r="J117">
+        <v>44390</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Abaddon II 7</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118">
+        <v>44513</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Abaddon II 8</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119">
+        <v>44647</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Abaddon II 9</v>
+      </c>
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>Rider Block</v>
+      </c>
+      <c r="J120">
+        <v>44772</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Abaddon II 10</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121">
+        <v>44856</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Abaddon II Ultra-Enhance</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122">
+        <v>44938</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Abaddon III 1</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123">
+        <v>44590</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Abaddon III 2</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124">
+        <v>45070</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Abaddon III 3</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125">
+        <v>45191</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Abaddon III 4</v>
+      </c>
+      <c r="B126" t="str">
+        <v/>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>Thermal Insulation</v>
+      </c>
+      <c r="J126">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Abaddon III 5</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127">
+        <v>45445</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Abaddon III 6</v>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128">
+        <v>45513</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Abaddon III 7</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129">
+        <v>45592</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Abaddon III 8</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130">
+        <v>45716</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Abaddon III 9</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131">
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Abaddon III 10</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v>Ray Dilution</v>
+      </c>
+      <c r="J132">
+        <v>45978</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J132"/>
   </ignoredErrors>
 </worksheet>
 </file>